--- a/reports/devops-juniors-israel-2026-W43.xlsx
+++ b/reports/devops-juniors-israel-2026-W43.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="321">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-19T12:57:18</t>
+    <t xml:space="preserve">2026-10-20T11:25:18</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -94,12 +94,12 @@
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
@@ -250,87 +250,75 @@
     <t xml:space="preserve">2026-10-15</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
   </si>
   <si>
@@ -364,6 +352,24 @@
     <t xml:space="preserve">2026-08-18</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New York City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7995568003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-20</t>
+  </si>
+  <si>
     <t xml:space="preserve">Security Analyst (Student Position)</t>
   </si>
   <si>
@@ -466,210 +472,195 @@
     <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Databases, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-agas-4478292095</t>
+    <t xml:space="preserve">Junior Developer, Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppCard, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-developer-core-platform-at-appcard-inc-4477317181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Physicist / System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEQA Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-physicist-system-engineer-at-heqa-security-4477785774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (1006801)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4479783873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hozek Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (37577)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4480984028</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-19</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Developer, Core Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppCard, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-developer-core-platform-at-appcard-inc-4477317181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Physicist / System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEQA Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-physicist-system-engineer-at-heqa-security-4477785774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (1006801)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4479783873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hozek Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (37577)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4480984028</t>
-  </si>
-  <si>
     <t xml:space="preserve">abra</t>
   </si>
   <si>
@@ -682,6 +673,18 @@
     <t xml:space="preserve">2026-08-19</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux System Administrator (5522)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-5522-at-ingima-4481550711</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
   </si>
   <si>
@@ -733,6 +736,21 @@
     <t xml:space="preserve">2026-10-14</t>
   </si>
   <si>
+    <t xml:space="preserve">Soc Tier 1(25822)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/soc-tier-1-25822-at-yael-group-4478266623</t>
+  </si>
+  <si>
     <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
   </si>
   <si>
@@ -853,13 +871,19 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
@@ -868,12 +892,6 @@
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
@@ -931,10 +949,10 @@
     <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
   </si>
   <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
@@ -1083,7 +1101,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -1099,7 +1117,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -1107,7 +1125,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -1189,7 +1207,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1197,7 +1215,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -1255,7 +1273,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1323,7 +1341,7 @@
         <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1419,7 +1437,7 @@
         <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
@@ -1512,25 +1530,25 @@
         <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -1538,31 +1556,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -1570,31 +1588,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">
@@ -1626,7 +1644,7 @@
         <v>99</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -1634,31 +1652,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F12" s="3">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13">
@@ -1666,31 +1684,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -1698,31 +1716,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15">
@@ -1730,31 +1748,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F15" s="3">
         <v>74</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -1762,28 +1780,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F16" s="3">
         <v>70</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>67</v>
@@ -1794,7 +1812,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>63</v>
@@ -1803,22 +1821,22 @@
         <v>64</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F17" s="3">
         <v>70</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -1826,13 +1844,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
@@ -1841,16 +1859,16 @@
         <v>68</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19">
@@ -1858,31 +1876,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
         <v>61</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20">
@@ -1890,13 +1908,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>28</v>
@@ -1905,16 +1923,16 @@
         <v>57</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21">
@@ -1922,13 +1940,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>28</v>
@@ -1937,16 +1955,16 @@
         <v>46</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22">
@@ -1954,31 +1972,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F22" s="3">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23">
@@ -1986,31 +2004,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F23" s="3">
         <v>41</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24">
@@ -2018,31 +2036,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>167</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25">
@@ -2050,19 +2068,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>171</v>
@@ -2074,7 +2092,7 @@
         <v>172</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>67</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26">
@@ -2082,31 +2100,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2159,7 +2177,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -2174,22 +2192,22 @@
         <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2">
@@ -2203,7 +2221,7 @@
         <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2212,7 +2230,7 @@
         <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>33</v>
@@ -2224,7 +2242,7 @@
         <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2247,7 +2265,7 @@
         <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2259,7 +2277,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -2282,7 +2300,7 @@
         <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2294,7 +2312,7 @@
         <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -2308,7 +2326,7 @@
         <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
@@ -2317,7 +2335,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2329,7 +2347,7 @@
         <v>67</v>
       </c>
       <c r="K5" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -2352,7 +2370,7 @@
         <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2364,7 +2382,7 @@
         <v>67</v>
       </c>
       <c r="K6" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
@@ -2387,7 +2405,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2399,7 +2417,7 @@
         <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -2410,101 +2428,101 @@
         <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K8" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E9" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K9" s="3">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="K10" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -2527,7 +2545,7 @@
         <v>98</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2536,190 +2554,190 @@
         <v>99</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="K11" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E12" s="3">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="K12" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>11</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K14" s="3">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E15" s="3">
         <v>74</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E16" s="3">
         <v>70</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>67</v>
       </c>
       <c r="K16" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>63</v>
@@ -2728,39 +2746,39 @@
         <v>64</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E17" s="3">
         <v>70</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K17" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
@@ -2769,68 +2787,68 @@
         <v>68</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K18" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
         <v>61</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K19" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>28</v>
@@ -2839,33 +2857,33 @@
         <v>57</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="K20" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>28</v>
@@ -2874,150 +2892,150 @@
         <v>46</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K21" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E22" s="3">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E23" s="3">
         <v>41</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K23" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>167</v>
+        <v>67</v>
       </c>
       <c r="K24" s="3">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
@@ -3026,91 +3044,91 @@
         <v>172</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>67</v>
+        <v>173</v>
       </c>
       <c r="K25" s="3">
-        <v>60</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="K26" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>185</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3">
+        <v>28</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="3">
-        <v>34</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="K27" s="3">
-        <v>12</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>189</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>58</v>
+        <v>190</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
@@ -3119,138 +3137,138 @@
         <v>28</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K28" s="3">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E29" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K29" s="3">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
         <v>27</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>94</v>
+        <v>203</v>
       </c>
       <c r="K30" s="3">
-        <v>14</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K31" s="3">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>210</v>
+        <v>148</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
@@ -3259,33 +3277,33 @@
         <v>24</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K32" s="3">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>215</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
@@ -3297,7 +3315,7 @@
         <v>216</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>32</v>
@@ -3306,21 +3324,21 @@
         <v>217</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>155</v>
+        <v>218</v>
       </c>
       <c r="K33" s="3">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>173</v>
+        <v>219</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3329,243 +3347,243 @@
         <v>24</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>221</v>
+        <v>117</v>
       </c>
       <c r="K34" s="3">
-        <v>61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E35" s="3">
         <v>23</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K35" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3">
         <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K36" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E37" s="3">
         <v>20</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K37" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>170</v>
+        <v>242</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E38" s="3">
         <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>207</v>
+        <v>117</v>
       </c>
       <c r="K38" s="3">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>83</v>
+        <v>245</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E39" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>49</v>
+        <v>203</v>
       </c>
       <c r="K39" s="3">
-        <v>6</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>246</v>
+        <v>78</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>155</v>
+        <v>49</v>
       </c>
       <c r="K40" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
@@ -3574,68 +3592,68 @@
         <v>12</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K41" s="3">
-        <v>66</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>173</v>
+        <v>256</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>97</v>
+        <v>166</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>161</v>
+        <v>203</v>
       </c>
       <c r="K42" s="3">
-        <v>3</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>257</v>
+        <v>169</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>199</v>
+        <v>92</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
@@ -3644,57 +3662,57 @@
         <v>8</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>49</v>
+        <v>157</v>
       </c>
       <c r="K43" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" s="3">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E44" s="3">
-        <v>4</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>263</v>
-      </c>
       <c r="G44" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>265</v>
+        <v>49</v>
       </c>
       <c r="K44" s="3">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -3708,30 +3726,65 @@
         <v>268</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="G45" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K45" s="3">
-        <v>82</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="K46" s="3">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K45"/>
+  <autoFilter ref="A1:K46"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3777,6 +3830,7 @@
     <hyperlink ref="I43" r:id="rId42"/>
     <hyperlink ref="I44" r:id="rId43"/>
     <hyperlink ref="I45" r:id="rId44"/>
+    <hyperlink ref="I46" r:id="rId45"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3784,9 +3838,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3807,10 +3861,10 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>43</v>
@@ -3818,33 +3872,33 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
@@ -3853,36 +3907,36 @@
         <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -3905,178 +3959,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B4" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="B5" s="3">
         <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B8" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B9" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B12" s="3">
         <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B13" s="3">
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B14" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B16" s="3">
         <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -4096,10 +4150,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2">
@@ -4107,10 +4161,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3">
@@ -4118,10 +4172,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4">
@@ -4132,7 +4186,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5">
@@ -4143,7 +4197,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6">
@@ -4154,7 +4208,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7">
@@ -4165,7 +4219,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -4186,13 +4240,13 @@
         <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2">
@@ -4200,10 +4254,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4215,19 +4269,19 @@
         <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W43.xlsx
+++ b/reports/devops-juniors-israel-2026-W43.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="320">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-20T11:25:18</t>
+    <t xml:space="preserve">2026-10-21T11:40:08</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -250,6 +250,21 @@
     <t xml:space="preserve">2026-10-15</t>
   </si>
   <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
@@ -316,9 +331,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
   </si>
   <si>
@@ -382,7 +394,7 @@
     <t xml:space="preserve">System Integration Student, SPIV team</t>
   </si>
   <si>
-    <t xml:space="preserve">Amazon</t>
+    <t xml:space="preserve">Annapurna Labs</t>
   </si>
   <si>
     <t xml:space="preserve">Haifa, Haifa District, Israel</t>
@@ -391,7 +403,7 @@
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-student-spiv-team-at-amazon-4456348779</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-student-spiv-team-at-annapurna-labs-4456348779</t>
   </si>
   <si>
     <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
@@ -538,6 +550,24 @@
     <t xml:space="preserve">2026-10-12</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Service Desk Team Leader</t>
   </si>
   <si>
@@ -553,24 +583,6 @@
     <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gini-Apps</t>
   </si>
   <si>
@@ -580,19 +592,22 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Operator (1006801)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4479783873</t>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-ngsoft-4478985179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-21</t>
   </si>
   <si>
     <t xml:space="preserve">Junior System Administrator</t>
@@ -601,9 +616,6 @@
     <t xml:space="preserve">Hozek Technologies Ltd.</t>
   </si>
   <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
   </si>
   <si>
@@ -685,6 +697,12 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-5522-at-ingima-4481550711</t>
   </si>
   <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-group-4478686628</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
   </si>
   <si>
@@ -700,24 +718,6 @@
     <t xml:space="preserve">2026-09-11</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-29</t>
-  </si>
-  <si>
     <t xml:space="preserve">Technical Support Engineer- Tier 3</t>
   </si>
   <si>
@@ -739,9 +739,6 @@
     <t xml:space="preserve">Soc Tier 1(25822)</t>
   </si>
   <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
   </si>
   <si>
@@ -868,12 +865,12 @@
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
@@ -910,16 +907,16 @@
     <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
@@ -1101,7 +1098,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -1109,7 +1106,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1125,7 +1122,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -1207,7 +1204,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -1215,7 +1212,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -1265,7 +1262,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30">
@@ -1273,7 +1270,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1530,25 +1527,25 @@
         <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -1556,31 +1553,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="3">
+        <v>96</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -1588,31 +1585,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="3">
+        <v>88</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="3">
-        <v>84</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="11">
@@ -1644,7 +1641,7 @@
         <v>99</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -1652,31 +1649,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3">
+        <v>84</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="3">
-        <v>83</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -1684,31 +1681,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="3">
+        <v>83</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="3">
-        <v>80</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -1716,31 +1713,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="3">
+        <v>80</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="3">
-        <v>78</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="15">
@@ -1748,31 +1745,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>119</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>120</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -1780,31 +1777,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
@@ -1812,13 +1809,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="D17" s="3" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1827,16 +1824,16 @@
         <v>70</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18">
@@ -1847,28 +1844,28 @@
         <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3">
+        <v>70</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="3">
-        <v>68</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="19">
@@ -1876,31 +1873,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="3">
+        <v>68</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="3">
-        <v>61</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="20">
@@ -1908,31 +1905,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="3">
+        <v>61</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="3">
-        <v>57</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="21">
@@ -1940,31 +1937,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F21" s="3">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22">
@@ -1972,31 +1969,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F22" s="3">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="23">
@@ -2004,31 +2001,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="E23" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F23" s="3">
         <v>41</v>
       </c>
       <c r="G23" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="24">
@@ -2036,31 +2033,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="E24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="3">
+        <v>41</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="3">
-        <v>39</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="25">
@@ -2068,19 +2065,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>171</v>
@@ -2092,7 +2089,7 @@
         <v>172</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>173</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26">
@@ -2100,31 +2097,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="3">
+        <v>36</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="3">
-        <v>34</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2177,7 +2174,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -2192,22 +2189,22 @@
         <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2">
@@ -2230,7 +2227,7 @@
         <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>33</v>
@@ -2242,7 +2239,7 @@
         <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2265,7 +2262,7 @@
         <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2277,7 +2274,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -2300,7 +2297,7 @@
         <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2312,7 +2309,7 @@
         <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
@@ -2335,7 +2332,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2347,7 +2344,7 @@
         <v>67</v>
       </c>
       <c r="K5" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -2370,7 +2367,7 @@
         <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2382,7 +2379,7 @@
         <v>67</v>
       </c>
       <c r="K6" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
@@ -2405,7 +2402,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2417,7 +2414,7 @@
         <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -2428,101 +2425,101 @@
         <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="K8" s="3">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="3">
+        <v>96</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="K9" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="3">
+        <v>88</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="3">
-        <v>84</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K10" s="3">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -2545,7 +2542,7 @@
         <v>98</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2554,196 +2551,196 @@
         <v>99</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="K11" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>84</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="3">
-        <v>83</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="K12" s="3">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="3">
+        <v>83</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3">
-        <v>80</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="K13" s="3">
-        <v>63</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3">
+        <v>80</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="3">
-        <v>78</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>119</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>120</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="K15" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E16" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="K16" s="3">
-        <v>61</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="C17" s="3" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>27</v>
@@ -2752,22 +2749,22 @@
         <v>70</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="K17" s="3">
-        <v>13</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -2775,267 +2772,267 @@
         <v>130</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="3">
+        <v>70</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3">
-        <v>68</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="K18" s="3">
-        <v>46</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="3">
+        <v>68</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="3">
-        <v>61</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="K19" s="3">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="3">
+        <v>61</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="3">
-        <v>57</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="K20" s="3">
-        <v>12</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E21" s="3">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="K21" s="3">
-        <v>55</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E22" s="3">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="K22" s="3">
-        <v>4</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="D23" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E23" s="3">
         <v>41</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="K23" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="D24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="3">
+        <v>41</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="3">
-        <v>39</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="K24" s="3">
-        <v>61</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E25" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
@@ -3044,91 +3041,91 @@
         <v>172</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>173</v>
+        <v>67</v>
       </c>
       <c r="K25" s="3">
-        <v>8</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="3">
+        <v>36</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="3">
-        <v>34</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="K26" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>185</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>58</v>
+        <v>186</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="K27" s="3">
-        <v>61</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>189</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>190</v>
+        <v>58</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
@@ -3137,57 +3134,57 @@
         <v>28</v>
       </c>
       <c r="F28" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="K28" s="3">
-        <v>5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>28</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E29" s="3">
-        <v>27</v>
-      </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="3" t="s">
+      <c r="J29" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="K29" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3198,77 +3195,77 @@
         <v>199</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E30" s="3">
         <v>27</v>
       </c>
       <c r="F30" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="J30" s="3" t="s">
-        <v>203</v>
+        <v>94</v>
       </c>
       <c r="K30" s="3">
-        <v>67</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="D31" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="3">
+        <v>27</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="3">
-        <v>24</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="K31" s="3">
-        <v>48</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
@@ -3277,33 +3274,33 @@
         <v>24</v>
       </c>
       <c r="F32" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="K32" s="3">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>169</v>
+        <v>214</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>215</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
@@ -3315,7 +3312,7 @@
         <v>216</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>32</v>
@@ -3327,18 +3324,18 @@
         <v>218</v>
       </c>
       <c r="K33" s="3">
-        <v>62</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="C34" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3347,22 +3344,22 @@
         <v>24</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="3" t="s">
+      <c r="J34" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="J34" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="K34" s="3">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35">
@@ -3373,19 +3370,19 @@
         <v>224</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>225</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>32</v>
@@ -3394,91 +3391,91 @@
         <v>226</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>227</v>
+        <v>121</v>
       </c>
       <c r="K35" s="3">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="3">
+        <v>24</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="3">
-        <v>20</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="J36" s="3" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="K36" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>236</v>
+        <v>58</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E37" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="K37" s="3">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>26</v>
@@ -3487,33 +3484,33 @@
         <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>117</v>
+        <v>239</v>
       </c>
       <c r="K38" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>166</v>
+        <v>241</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>26</v>
@@ -3522,103 +3519,103 @@
         <v>20</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>203</v>
+        <v>121</v>
       </c>
       <c r="K39" s="3">
-        <v>67</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E40" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>49</v>
+        <v>207</v>
       </c>
       <c r="K40" s="3">
-        <v>7</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>252</v>
+        <v>83</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>214</v>
+        <v>49</v>
       </c>
       <c r="K41" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
@@ -3627,68 +3624,68 @@
         <v>12</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="K42" s="3">
-        <v>67</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>169</v>
+        <v>255</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>92</v>
+        <v>170</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>157</v>
+        <v>207</v>
       </c>
       <c r="K43" s="3">
-        <v>4</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>263</v>
+        <v>173</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>195</v>
+        <v>97</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3697,94 +3694,129 @@
         <v>8</v>
       </c>
       <c r="F44" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>265</v>
-      </c>
       <c r="J44" s="3" t="s">
-        <v>49</v>
+        <v>161</v>
       </c>
       <c r="K44" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>268</v>
+        <v>194</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>271</v>
+        <v>49</v>
       </c>
       <c r="K45" s="3">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
-      </c>
-      <c r="F46" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>268</v>
+      </c>
       <c r="G46" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I46" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="K46" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="J47" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="K46" s="3">
-        <v>83</v>
+      <c r="K47" s="3">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K46"/>
+  <autoFilter ref="A1:K47"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3831,6 +3863,7 @@
     <hyperlink ref="I44" r:id="rId43"/>
     <hyperlink ref="I45" r:id="rId44"/>
     <hyperlink ref="I46" r:id="rId45"/>
+    <hyperlink ref="I47" r:id="rId46"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3838,9 +3871,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3861,10 +3894,10 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>43</v>
@@ -3872,33 +3905,33 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>112</v>
+        <v>192</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>113</v>
+        <v>193</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>116</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>117</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>219</v>
+        <v>83</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
@@ -3907,44 +3940,20 @@
         <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="3">
-        <v>20</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>117</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G3"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3959,178 +3968,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2" s="3">
+        <v>31</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="B2" s="3">
-        <v>30</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B3" s="3">
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B6" s="3">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>286</v>
-      </c>
-      <c r="B6" s="3">
-        <v>23</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B7" s="3">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>288</v>
-      </c>
-      <c r="B7" s="3">
-        <v>22</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B8" s="3">
         <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B9" s="3">
         <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B10" s="3">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="B10" s="3">
-        <v>12</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B11" s="3">
+        <v>13</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="B11" s="3">
-        <v>12</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B12" s="3">
         <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B13" s="3">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="B13" s="3">
-        <v>11</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B14" s="3">
         <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B15" s="3">
+        <v>9</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="B15" s="3">
-        <v>8</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B16" s="3">
+        <v>9</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="B16" s="3">
-        <v>8</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -4150,10 +4159,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="2">
@@ -4161,10 +4170,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3">
@@ -4172,10 +4181,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4">
@@ -4186,7 +4195,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5">
@@ -4197,7 +4206,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6">
@@ -4208,7 +4217,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7">
@@ -4219,7 +4228,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -4240,13 +4249,13 @@
         <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="2">
@@ -4254,10 +4263,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4266,22 +4275,22 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W43.xlsx
+++ b/reports/devops-juniors-israel-2026-W43.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-21T11:40:08</t>
+    <t xml:space="preserve">2026-10-22T11:40:52</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -94,21 +94,18 @@
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -184,48 +181,33 @@
     <t xml:space="preserve">2026-09-16</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -316,21 +298,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
   </si>
   <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
   </si>
   <si>
@@ -466,6 +433,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
   </si>
   <si>
+    <t xml:space="preserve">Network Operations Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4482446270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-22</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
   </si>
   <si>
@@ -550,6 +535,21 @@
     <t xml:space="preserve">2026-10-12</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Service Desk Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
@@ -568,21 +568,6 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Service Desk Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gini-Apps</t>
   </si>
   <si>
@@ -592,195 +577,150 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NGsoft</t>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hozek Technologies Ltd.</t>
   </si>
   <si>
     <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-ngsoft-4478985179</t>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-group-4478686628</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hozek Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (37577)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4480984028</t>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer- Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Databases, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8176664?gh_jid=8176664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-sela-4476440697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4478250542</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-19</t>
   </si>
   <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator (5522)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-5522-at-ingima-4481550711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-group-4478686628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer- Tier 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Databases, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8176664?gh_jid=8176664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soc Tier 1(25822)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/soc-tier-1-25822-at-yael-group-4478266623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-sela-4476440697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4478250542</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Israel</t>
   </si>
   <si>
@@ -865,18 +805,18 @@
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
@@ -895,18 +835,18 @@
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
@@ -946,19 +886,16 @@
     <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1098,7 +1035,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -1106,7 +1043,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1114,7 +1051,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1122,7 +1059,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -1204,7 +1141,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -1212,7 +1149,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -1240,36 +1177,28 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3"/>
       <c r="B27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="3"/>
+      <c r="B28" s="3">
+        <v>34</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" s="3">
         <v>7</v>
       </c>
     </row>
@@ -1294,34 +1223,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1329,31 +1258,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -1361,13 +1290,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>25</v>
@@ -1376,16 +1305,16 @@
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -1393,31 +1322,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -1425,31 +1354,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -1457,13 +1386,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
@@ -1472,16 +1401,16 @@
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -1495,7 +1424,7 @@
         <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>25</v>
@@ -1504,16 +1433,16 @@
         <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1521,25 +1450,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>81</v>
@@ -1562,16 +1491,16 @@
         <v>85</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>86</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>87</v>
@@ -1594,22 +1523,22 @@
         <v>91</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>92</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -1617,31 +1546,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="3">
+        <v>83</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="3">
-        <v>84</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -1655,25 +1584,25 @@
         <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -1693,7 +1622,7 @@
         <v>27</v>
       </c>
       <c r="F13" s="3">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>108</v>
@@ -1716,28 +1645,28 @@
         <v>111</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="3">
+        <v>74</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="3">
-        <v>80</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
@@ -1745,31 +1674,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -1777,31 +1706,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="3">
+        <v>70</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="3">
-        <v>74</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="17">
@@ -1809,31 +1738,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="3">
+        <v>68</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="3">
-        <v>70</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18">
@@ -1841,25 +1770,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F18" s="3">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>131</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>132</v>
@@ -1882,22 +1811,22 @@
         <v>136</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F19" s="3">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>137</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>138</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20">
@@ -1905,25 +1834,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>142</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>143</v>
@@ -1949,19 +1878,19 @@
         <v>28</v>
       </c>
       <c r="F21" s="3">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>148</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>149</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22">
@@ -1969,31 +1898,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F22" s="3">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23">
@@ -2001,31 +1930,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F23" s="3">
         <v>41</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24">
@@ -2033,31 +1962,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>167</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25">
@@ -2071,25 +2000,25 @@
         <v>169</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="3">
+        <v>36</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="3">
-        <v>39</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="26">
@@ -2103,25 +2032,25 @@
         <v>174</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F26" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>177</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2160,7 +2089,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2177,16 +2106,16 @@
         <v>178</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>179</v>
@@ -2195,13 +2124,13 @@
         <v>180</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>181</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>182</v>
@@ -2209,48 +2138,48 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K2" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>25</v>
@@ -2259,103 +2188,103 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="K3" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="K4" s="3">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="K5" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
@@ -2364,22 +2293,22 @@
         <v>100</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="K6" s="3">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -2390,7 +2319,7 @@
         <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>25</v>
@@ -2399,39 +2328,39 @@
         <v>100</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="K7" s="3">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>80</v>
@@ -2440,7 +2369,7 @@
         <v>183</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>81</v>
@@ -2449,7 +2378,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -2463,10 +2392,10 @@
         <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E9" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>86</v>
@@ -2475,7 +2404,7 @@
         <v>183</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>87</v>
@@ -2484,7 +2413,7 @@
         <v>88</v>
       </c>
       <c r="K9" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -2498,10 +2427,10 @@
         <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>92</v>
@@ -2510,51 +2439,51 @@
         <v>183</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="K10" s="3">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="3">
+        <v>83</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="3">
-        <v>84</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K11" s="3">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -2565,31 +2494,31 @@
         <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="K12" s="3">
-        <v>21</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -2606,7 +2535,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="3">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>108</v>
@@ -2624,7 +2553,7 @@
         <v>110</v>
       </c>
       <c r="K13" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -2632,124 +2561,124 @@
         <v>111</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="3">
+        <v>74</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="3">
-        <v>80</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="K14" s="3">
-        <v>64</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="K15" s="3">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="K16" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="D17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="3">
+        <v>68</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="3">
-        <v>70</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>183</v>
@@ -2758,30 +2687,30 @@
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="K17" s="3">
-        <v>62</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E18" s="3">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>131</v>
@@ -2790,7 +2719,7 @@
         <v>183</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>132</v>
@@ -2799,7 +2728,7 @@
         <v>133</v>
       </c>
       <c r="K18" s="3">
-        <v>14</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
@@ -2813,10 +2742,10 @@
         <v>136</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E19" s="3">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>137</v>
@@ -2825,33 +2754,33 @@
         <v>183</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>138</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="K19" s="3">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>142</v>
@@ -2860,7 +2789,7 @@
         <v>183</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>143</v>
@@ -2869,7 +2798,7 @@
         <v>144</v>
       </c>
       <c r="K20" s="3">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2886,7 +2815,7 @@
         <v>28</v>
       </c>
       <c r="E21" s="3">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>148</v>
@@ -2895,121 +2824,121 @@
         <v>183</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>149</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="K21" s="3">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E22" s="3">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K22" s="3">
-        <v>56</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E23" s="3">
         <v>41</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K23" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>167</v>
+        <v>60</v>
       </c>
       <c r="K24" s="3">
-        <v>3</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25">
@@ -3020,31 +2949,31 @@
         <v>169</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="3">
+        <v>36</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="3">
-        <v>39</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="K25" s="3">
-        <v>62</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -3055,16 +2984,16 @@
         <v>174</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E26" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>183</v>
@@ -3073,65 +3002,65 @@
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>177</v>
+        <v>122</v>
       </c>
       <c r="K26" s="3">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3">
+        <v>28</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="3">
-        <v>34</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="K27" s="3">
-        <v>14</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E28" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>190</v>
@@ -3140,16 +3069,16 @@
         <v>183</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>191</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="K28" s="3">
-        <v>62</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
@@ -3163,10 +3092,10 @@
         <v>194</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E29" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>195</v>
@@ -3175,7 +3104,7 @@
         <v>183</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>196</v>
@@ -3184,7 +3113,7 @@
         <v>197</v>
       </c>
       <c r="K29" s="3">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30">
@@ -3195,48 +3124,48 @@
         <v>199</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>94</v>
+        <v>203</v>
       </c>
       <c r="K30" s="3">
-        <v>16</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>204</v>
+        <v>147</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>205</v>
@@ -3245,7 +3174,7 @@
         <v>183</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>206</v>
@@ -3254,18 +3183,18 @@
         <v>207</v>
       </c>
       <c r="K31" s="3">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="C32" s="3" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
@@ -3274,74 +3203,74 @@
         <v>24</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K32" s="3">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" s="3">
+        <v>23</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="3">
-        <v>24</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K33" s="3">
-        <v>2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E34" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>220</v>
@@ -3359,7 +3288,7 @@
         <v>222</v>
       </c>
       <c r="K34" s="3">
-        <v>63</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
@@ -3370,13 +3299,13 @@
         <v>224</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E35" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>225</v>
@@ -3385,103 +3314,103 @@
         <v>183</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>226</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>121</v>
+        <v>197</v>
       </c>
       <c r="K35" s="3">
-        <v>1</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>227</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>194</v>
+        <v>147</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>197</v>
+        <v>48</v>
       </c>
       <c r="K36" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K37" s="3">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>236</v>
+        <v>165</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>237</v>
@@ -3490,106 +3419,106 @@
         <v>183</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>238</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>239</v>
+        <v>197</v>
       </c>
       <c r="K38" s="3">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="3">
+        <v>8</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" s="3">
-        <v>20</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="K39" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>183</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>207</v>
+        <v>48</v>
       </c>
       <c r="K40" s="3">
-        <v>68</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>83</v>
+        <v>245</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" s="3">
-        <v>16</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>249</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>183</v>
@@ -3598,13 +3527,13 @@
         <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J41" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K41" s="3">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
@@ -3615,17 +3544,15 @@
         <v>252</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>152</v>
+        <v>253</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E42" s="3">
-        <v>12</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>253</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>183</v>
       </c>
@@ -3636,187 +3563,14 @@
         <v>254</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="K42" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E43" s="3">
-        <v>12</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="K43" s="3">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E44" s="3">
-        <v>8</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="K44" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E45" s="3">
-        <v>8</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K45" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E46" s="3">
-        <v>4</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="K46" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="K47" s="3">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K47"/>
+  <autoFilter ref="A1:K42"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3859,11 +3613,6 @@
     <hyperlink ref="I40" r:id="rId39"/>
     <hyperlink ref="I41" r:id="rId40"/>
     <hyperlink ref="I42" r:id="rId41"/>
-    <hyperlink ref="I43" r:id="rId42"/>
-    <hyperlink ref="I44" r:id="rId43"/>
-    <hyperlink ref="I45" r:id="rId44"/>
-    <hyperlink ref="I46" r:id="rId45"/>
-    <hyperlink ref="I47" r:id="rId46"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3871,8 +3620,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -3882,16 +3631,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>179</v>
@@ -3900,60 +3649,36 @@
         <v>181</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>193</v>
+        <v>140</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>142</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>143</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="3">
-        <v>24</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>197</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G2"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F3" r:id="rId2"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3968,178 +3693,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="B2" s="3">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="B3" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>285</v>
+        <v>237</v>
       </c>
       <c r="B6" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="B7" s="3">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="B10" s="3">
         <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="B15" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="B16" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -4156,13 +3881,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2">
@@ -4170,10 +3895,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3">
@@ -4181,10 +3906,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4">
@@ -4195,7 +3920,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5">
@@ -4206,7 +3931,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6">
@@ -4217,18 +3942,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="3">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -4246,51 +3960,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>317</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3">
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W43.xlsx
+++ b/reports/devops-juniors-israel-2026-W43.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="298">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-22T11:40:52</t>
+    <t xml:space="preserve">2026-10-23T11:30:13</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -298,6 +298,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
   </si>
   <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471963869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-23</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
   </si>
   <si>
@@ -331,24 +349,6 @@
     <t xml:space="preserve">2026-08-18</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7995568003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-20</t>
-  </si>
-  <si>
     <t xml:space="preserve">Security Analyst (Student Position)</t>
   </si>
   <si>
@@ -403,6 +403,39 @@
     <t xml:space="preserve">2026-09-04</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-abra-4467537853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Networking, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-medulla-4468207460</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
   </si>
   <si>
@@ -418,19 +451,34 @@
     <t xml:space="preserve">2026-08-31</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
+    <t xml:space="preserve">Linux System Administrator (37866)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-37866-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4482465747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator Tier 3 – IT Infrastructure &amp; Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-tier-3-%E2%80%93-it-infrastructure-cybersecurity-at-mornex-4474264582</t>
   </si>
   <si>
     <t xml:space="preserve">Network Operations Center</t>
@@ -439,9 +487,6 @@
     <t xml:space="preserve">Compie Technologies</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
   </si>
   <si>
@@ -457,9 +502,6 @@
     <t xml:space="preserve">OnCloud</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
   </si>
   <si>
@@ -469,22 +511,16 @@
     <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Developer, Core Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AppCard, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-developer-core-platform-at-appcard-inc-4477317181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-16</t>
+    <t xml:space="preserve">Network Operations &amp; Control Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Kubernetes, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-control-technician-at-log-on-software-4480039508</t>
   </si>
   <si>
     <t xml:space="preserve">Junior Physicist / System Engineer</t>
@@ -505,192 +541,153 @@
     <t xml:space="preserve">2026-10-18</t>
   </si>
   <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hozek Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (37577)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4482471524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer- Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Databases, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8176664?gh_jid=8176664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
   </si>
   <si>
     <t xml:space="preserve">Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hozek Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-group-4478686628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer- Tier 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Databases, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8176664?gh_jid=8176664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
   </si>
   <si>
@@ -793,6 +790,9 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
@@ -808,19 +808,22 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
@@ -829,12 +832,6 @@
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kubernetes</t>
   </si>
   <si>
@@ -847,6 +844,12 @@
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
@@ -859,22 +862,16 @@
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Terraform/IaC</t>
   </si>
   <si>
     <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
   </si>
   <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1035,7 +1032,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -1043,7 +1040,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1051,7 +1048,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -1059,7 +1056,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -1141,7 +1138,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -1149,7 +1146,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -1157,7 +1154,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1165,7 +1162,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1191,7 +1188,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
@@ -1199,7 +1196,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1211,7 +1208,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="47" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1555,10 +1552,10 @@
         <v>96</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>97</v>
@@ -1584,25 +1581,25 @@
         <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -1610,25 +1607,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>108</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>109</v>
@@ -1645,10 +1642,10 @@
         <v>111</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>26</v>
@@ -1776,25 +1773,25 @@
         <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19">
@@ -1802,7 +1799,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>135</v>
@@ -1811,10 +1808,10 @@
         <v>136</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>137</v>
@@ -1826,7 +1823,7 @@
         <v>138</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>99</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20">
@@ -1834,19 +1831,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>141</v>
+        <v>63</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F20" s="3">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>142</v>
@@ -1875,10 +1872,10 @@
         <v>147</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>148</v>
@@ -1890,7 +1887,7 @@
         <v>149</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22">
@@ -1898,31 +1895,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="3">
+        <v>48</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" s="3">
-        <v>41</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23">
@@ -1930,31 +1927,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="3">
+        <v>48</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F23" s="3">
-        <v>41</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="24">
@@ -1962,31 +1959,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="3">
+        <v>46</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F24" s="3">
-        <v>39</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="25">
@@ -1994,31 +1991,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="3">
+        <v>44</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="3">
-        <v>36</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>172</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26">
@@ -2026,31 +2023,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" s="3">
+        <v>41</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="3">
-        <v>34</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2089,7 +2086,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2103,7 +2100,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2118,22 +2115,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2">
@@ -2156,7 +2153,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2168,7 +2165,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2191,7 +2188,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2203,7 +2200,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -2226,7 +2223,7 @@
         <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2238,7 +2235,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
@@ -2261,7 +2258,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2273,7 +2270,7 @@
         <v>60</v>
       </c>
       <c r="K5" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -2296,7 +2293,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
@@ -2308,7 +2305,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -2331,7 +2328,7 @@
         <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
@@ -2343,7 +2340,7 @@
         <v>76</v>
       </c>
       <c r="K7" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -2366,7 +2363,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
@@ -2378,7 +2375,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -2401,7 +2398,7 @@
         <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
@@ -2413,7 +2410,7 @@
         <v>88</v>
       </c>
       <c r="K9" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -2436,7 +2433,7 @@
         <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
@@ -2448,7 +2445,7 @@
         <v>48</v>
       </c>
       <c r="K10" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -2462,16 +2459,16 @@
         <v>96</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
@@ -2483,7 +2480,7 @@
         <v>99</v>
       </c>
       <c r="K11" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2494,57 +2491,57 @@
         <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>65</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>109</v>
@@ -2553,7 +2550,7 @@
         <v>110</v>
       </c>
       <c r="K13" s="3">
-        <v>2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
@@ -2561,10 +2558,10 @@
         <v>111</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>26</v>
@@ -2576,7 +2573,7 @@
         <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
@@ -2588,7 +2585,7 @@
         <v>76</v>
       </c>
       <c r="K14" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -2611,7 +2608,7 @@
         <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
@@ -2623,7 +2620,7 @@
         <v>60</v>
       </c>
       <c r="K15" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -2646,7 +2643,7 @@
         <v>120</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
@@ -2658,7 +2655,7 @@
         <v>122</v>
       </c>
       <c r="K16" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -2681,7 +2678,7 @@
         <v>126</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -2693,7 +2690,7 @@
         <v>128</v>
       </c>
       <c r="K17" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -2704,36 +2701,36 @@
         <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K18" s="3">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>135</v>
@@ -2742,16 +2739,16 @@
         <v>136</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>137</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
@@ -2760,33 +2757,33 @@
         <v>138</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="K19" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>141</v>
+        <v>63</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E20" s="3">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>142</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
@@ -2798,7 +2795,7 @@
         <v>144</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21">
@@ -2812,16 +2809,16 @@
         <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>148</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
@@ -2830,193 +2827,193 @@
         <v>149</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="K21" s="3">
-        <v>57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3">
+        <v>48</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E22" s="3">
-        <v>41</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="K22" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="3">
+        <v>48</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E23" s="3">
-        <v>41</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="K23" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="3">
+        <v>46</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="3">
-        <v>39</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="K24" s="3">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="3">
+        <v>44</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="3">
-        <v>36</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>172</v>
+        <v>99</v>
       </c>
       <c r="K25" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="3">
+        <v>41</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="3">
-        <v>34</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="K26" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>63</v>
@@ -3025,176 +3022,176 @@
         <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="K27" s="3">
-        <v>63</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="3">
+        <v>34</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="3">
-        <v>27</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="K28" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>28</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="3">
-        <v>27</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>197</v>
+        <v>60</v>
       </c>
       <c r="K29" s="3">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="3">
+        <v>27</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" s="3">
-        <v>24</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="J30" s="3" t="s">
-        <v>203</v>
+        <v>88</v>
       </c>
       <c r="K30" s="3">
-        <v>50</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E31" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="K31" s="3">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
@@ -3203,103 +3200,103 @@
         <v>24</v>
       </c>
       <c r="F32" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="K32" s="3">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="3">
+        <v>24</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E33" s="3">
-        <v>23</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="J33" s="3" t="s">
-        <v>216</v>
+        <v>99</v>
       </c>
       <c r="K33" s="3">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>217</v>
+        <v>181</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>218</v>
+        <v>130</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>219</v>
+        <v>131</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K34" s="3">
-        <v>8</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>165</v>
+        <v>218</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>27</v>
@@ -3308,103 +3305,103 @@
         <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>197</v>
+        <v>139</v>
       </c>
       <c r="K35" s="3">
-        <v>69</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>147</v>
+        <v>223</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E36" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>48</v>
+        <v>203</v>
       </c>
       <c r="K36" s="3">
-        <v>9</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>230</v>
+        <v>77</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>234</v>
+        <v>48</v>
       </c>
       <c r="K37" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
@@ -3413,68 +3410,68 @@
         <v>12</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="K38" s="3">
-        <v>69</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>168</v>
+        <v>234</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>91</v>
+        <v>223</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>156</v>
+        <v>203</v>
       </c>
       <c r="K39" s="3">
-        <v>6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>242</v>
+        <v>181</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3483,94 +3480,129 @@
         <v>8</v>
       </c>
       <c r="F40" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="J40" s="3" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="K40" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>247</v>
+        <v>196</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>250</v>
+        <v>48</v>
       </c>
       <c r="K41" s="3">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>247</v>
+      </c>
       <c r="G42" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I42" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="K42" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="J43" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="K42" s="3">
-        <v>85</v>
+      <c r="K43" s="3">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K42"/>
+  <autoFilter ref="A1:K43"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3613,6 +3645,7 @@
     <hyperlink ref="I40" r:id="rId39"/>
     <hyperlink ref="I41" r:id="rId40"/>
     <hyperlink ref="I42" r:id="rId41"/>
+    <hyperlink ref="I43" r:id="rId42"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3620,8 +3653,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -3643,10 +3676,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -3654,31 +3687,127 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>139</v>
+        <v>94</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
+        <v>84</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="3">
+        <v>52</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3">
         <v>48</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>144</v>
+      <c r="E4" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>44</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>24</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
+    <hyperlink ref="F3" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
+    <hyperlink ref="F6" r:id="rId5"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3686,185 +3815,185 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="B5" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7" s="3">
+        <v>21</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="B7" s="3">
-        <v>19</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B8" s="3">
+        <v>19</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="B8" s="3">
-        <v>18</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B9" s="3">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="B9" s="3">
-        <v>17</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B10" s="3">
+        <v>14</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="B10" s="3">
-        <v>13</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B11" s="3">
+        <v>13</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="B11" s="3">
-        <v>12</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B12" s="3">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="B12" s="3">
-        <v>11</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B13" s="3">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="B13" s="3">
-        <v>11</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B14" s="3">
+        <v>10</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="B14" s="3">
-        <v>9</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B16" s="3">
         <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -3884,10 +4013,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="2">
@@ -3895,10 +4024,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3">
@@ -3906,10 +4035,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4">
@@ -3917,10 +4046,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5">
@@ -3928,10 +4057,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6">
@@ -3942,7 +4071,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -3963,13 +4092,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="2">
@@ -3977,10 +4106,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3989,22 +4118,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W43.xlsx
+++ b/reports/devops-juniors-israel-2026-W43.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-23T11:30:13</t>
+    <t xml:space="preserve">2026-10-25T11:15:37</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -106,6 +106,9 @@
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -265,6 +268,24 @@
     <t xml:space="preserve">2026-10-11</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior Backend &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Vault</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Cloud (any), Docker, CI/CD, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-backend-devops-engineer-at-the-vault-4481056311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-25</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
   </si>
   <si>
@@ -481,289 +502,268 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-tier-3-%E2%80%93-it-infrastructure-cybersecurity-at-mornex-4474264582</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Operations Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Kubernetes, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-technician-at-confidential-careers-4481091143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Physicist / System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEQA Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-physicist-system-engineer-at-heqa-security-4477785774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4481088252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hozek Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (37577)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4482471524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer- Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Databases, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8176664?gh_jid=8176664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4479110861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4478768786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
     <t xml:space="preserve">Network Operations Center</t>
   </si>
   <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4482446270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations &amp; Control Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Kubernetes, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-control-technician-at-log-on-software-4480039508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Physicist / System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEQA Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-physicist-system-engineer-at-heqa-security-4477785774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hozek Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (37577)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4482471524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer- Tier 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Databases, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8176664?gh_jid=8176664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-sela-4476440697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4478250542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4479110861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4478768786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01</t>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-yael-korentec-technologies-4483377323</t>
   </si>
   <si>
     <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
@@ -799,9 +799,6 @@
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
@@ -832,16 +829,22 @@
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kubernetes</t>
   </si>
   <si>
     <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
@@ -850,12 +853,6 @@
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
@@ -893,6 +890,9 @@
   </si>
   <si>
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1040,7 +1040,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1056,7 +1056,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>298</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -1138,7 +1138,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
@@ -1174,28 +1174,36 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="A27" s="3"/>
       <c r="B27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="3">
-        <v>36</v>
-      </c>
+      <c r="B28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="3">
         <v>6</v>
       </c>
     </row>
@@ -1220,34 +1228,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1255,13 +1263,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>27</v>
@@ -1270,16 +1278,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -1287,13 +1295,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>25</v>
@@ -1302,16 +1310,16 @@
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -1319,13 +1327,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>26</v>
@@ -1334,16 +1342,16 @@
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -1351,13 +1359,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>25</v>
@@ -1366,16 +1374,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -1383,13 +1391,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
@@ -1398,16 +1406,16 @@
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1415,13 +1423,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>25</v>
@@ -1430,16 +1438,16 @@
         <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1447,13 +1455,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
@@ -1462,16 +1470,16 @@
         <v>96</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -1479,31 +1487,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F9" s="3">
+        <v>89</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -1511,31 +1519,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F10" s="3">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -1543,13 +1551,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>25</v>
@@ -1558,16 +1566,16 @@
         <v>84</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -1575,31 +1583,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13">
@@ -1607,31 +1615,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14">
@@ -1639,31 +1647,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15">
@@ -1671,31 +1679,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16">
@@ -1703,13 +1711,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>26</v>
@@ -1718,16 +1726,16 @@
         <v>70</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
@@ -1735,31 +1743,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -1767,13 +1775,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
@@ -1782,16 +1790,16 @@
         <v>68</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19">
@@ -1799,31 +1807,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20">
@@ -1831,31 +1839,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21">
@@ -1863,31 +1871,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F21" s="3">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22">
@@ -1895,31 +1903,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23">
@@ -1927,13 +1935,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -1942,16 +1950,16 @@
         <v>48</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>159</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24">
@@ -1959,13 +1967,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>28</v>
@@ -1974,16 +1982,16 @@
         <v>46</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25">
@@ -1991,13 +1999,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
@@ -2006,16 +2014,16 @@
         <v>44</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26">
@@ -2023,13 +2031,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>29</v>
@@ -2038,16 +2046,16 @@
         <v>41</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -2100,48 +2108,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>27</v>
@@ -2150,33 +2158,33 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>25</v>
@@ -2185,33 +2193,33 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
@@ -2220,33 +2228,33 @@
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>25</v>
@@ -2255,33 +2263,33 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K5" s="3">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
@@ -2290,33 +2298,33 @@
         <v>100</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>25</v>
@@ -2325,33 +2333,33 @@
         <v>100</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
@@ -2360,103 +2368,103 @@
         <v>96</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K8" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E9" s="3">
+        <v>89</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K9" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E10" s="3">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="K10" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>25</v>
@@ -2465,173 +2473,173 @@
         <v>84</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K12" s="3">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K13" s="3">
-        <v>66</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="K14" s="3">
-        <v>23</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="K15" s="3">
-        <v>64</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>26</v>
@@ -2640,68 +2648,68 @@
         <v>70</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="K16" s="3">
-        <v>16</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K17" s="3">
-        <v>49</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
@@ -2710,54 +2718,54 @@
         <v>68</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K18" s="3">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K19" s="3">
         <v>9</v>
@@ -2765,118 +2773,118 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K20" s="3">
-        <v>53</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E21" s="3">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
@@ -2885,33 +2893,33 @@
         <v>48</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>159</v>
+        <v>106</v>
       </c>
       <c r="K23" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>28</v>
@@ -2920,33 +2928,33 @@
         <v>46</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K24" s="3">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
@@ -2955,19 +2963,19 @@
         <v>44</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
@@ -2975,13 +2983,13 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>29</v>
@@ -2990,33 +2998,33 @@
         <v>41</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K26" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
@@ -3025,141 +3033,141 @@
         <v>36</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K27" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3">
+        <v>36</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E28" s="3">
-        <v>34</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="K28" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>191</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>63</v>
+        <v>192</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E29" s="3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="K29" s="3">
-        <v>64</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>195</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3">
+        <v>28</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E30" s="3">
-        <v>27</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="J30" s="3" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="K30" s="3">
-        <v>18</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E31" s="3">
         <v>27</v>
@@ -3168,65 +3176,65 @@
         <v>201</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>202</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>203</v>
+        <v>95</v>
       </c>
       <c r="K31" s="3">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="3">
+        <v>27</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>24</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="K32" s="3">
-        <v>51</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
@@ -3238,30 +3246,30 @@
         <v>211</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>212</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>99</v>
+        <v>213</v>
       </c>
       <c r="K33" s="3">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3270,68 +3278,68 @@
         <v>24</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>215</v>
+        <v>106</v>
       </c>
       <c r="K34" s="3">
-        <v>65</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="3">
+        <v>24</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="G35" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E35" s="3">
-        <v>20</v>
-      </c>
-      <c r="F35" s="3" t="s">
+      <c r="J35" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="K35" s="3">
-        <v>9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>223</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>27</v>
@@ -3340,57 +3348,57 @@
         <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="J36" s="3" t="s">
-        <v>203</v>
+        <v>146</v>
       </c>
       <c r="K36" s="3">
-        <v>70</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>77</v>
+        <v>225</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>226</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E37" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>227</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>228</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>48</v>
+        <v>207</v>
       </c>
       <c r="K37" s="3">
-        <v>10</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38">
@@ -3401,7 +3409,7 @@
         <v>230</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
@@ -3413,65 +3421,65 @@
         <v>231</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>232</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="K38" s="3">
-        <v>4</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="3">
+        <v>8</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="G39" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="3">
-        <v>12</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>237</v>
-      </c>
       <c r="J39" s="3" t="s">
-        <v>203</v>
+        <v>141</v>
       </c>
       <c r="K39" s="3">
-        <v>70</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>181</v>
+        <v>236</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>91</v>
+        <v>200</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3480,92 +3488,92 @@
         <v>8</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>134</v>
+        <v>49</v>
       </c>
       <c r="K40" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="D41" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" s="3">
-        <v>8</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>239</v>
-      </c>
       <c r="G41" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>243</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
       <c r="K41" s="3">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E42" s="3">
         <v>4</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>249</v>
+        <v>89</v>
       </c>
       <c r="K42" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3586,10 +3594,10 @@
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>253</v>
@@ -3598,7 +3606,7 @@
         <v>254</v>
       </c>
       <c r="K43" s="3">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -3653,8 +3661,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -3664,150 +3672,126 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D2" s="3">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>165</v>
+        <v>245</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>166</v>
+        <v>246</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>167</v>
+        <v>248</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>168</v>
+        <v>249</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>24</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3833,7 +3817,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B2" s="3">
         <v>26</v>
@@ -3855,145 +3839,145 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B4" s="3">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="B4" s="3">
-        <v>25</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B5" s="3">
         <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B6" s="3">
         <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B7" s="3">
         <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B8" s="3">
         <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B9" s="3">
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B10" s="3">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="B10" s="3">
-        <v>14</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B11" s="3">
         <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B12" s="3">
         <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B13" s="3">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>278</v>
-      </c>
-      <c r="B13" s="3">
-        <v>10</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B14" s="3">
+        <v>11</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="B14" s="3">
-        <v>10</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B16" s="3">
         <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -4010,13 +3994,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="2">
@@ -4024,10 +4008,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3">
@@ -4038,7 +4022,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4">
@@ -4049,7 +4033,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5">
@@ -4060,7 +4044,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6">
@@ -4071,6 +4055,17 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>292</v>
       </c>
     </row>
@@ -4089,7 +4084,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>293</v>
@@ -4103,7 +4098,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3">
         <v>6</v>
@@ -4115,7 +4110,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3">
         <v>39</v>
